--- a/data/analysis_panns/sound_class_eval_panns_w5_0s_h2_5s.xlsx
+++ b/data/analysis_panns/sound_class_eval_panns_w5_0s_h2_5s.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="25">
   <si>
     <t>class</t>
   </si>
@@ -54,15 +54,6 @@
     <t>support</t>
   </si>
   <si>
-    <t>animal</t>
-  </si>
-  <si>
-    <t>burst_pop</t>
-  </si>
-  <si>
-    <t>door</t>
-  </si>
-  <si>
     <t>engine</t>
   </si>
   <si>
@@ -75,22 +66,13 @@
     <t>horn</t>
   </si>
   <si>
-    <t>horse</t>
-  </si>
-  <si>
     <t>impact</t>
   </si>
   <si>
-    <t>music</t>
-  </si>
-  <si>
     <t>shout</t>
   </si>
   <si>
     <t>skidding</t>
-  </si>
-  <si>
-    <t>speech</t>
   </si>
   <si>
     <t>tire_squeal</t>
@@ -478,7 +460,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H15"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -512,25 +494,25 @@
         <v>8</v>
       </c>
       <c r="B2">
-        <v>0</v>
+        <v>0.625</v>
       </c>
       <c r="C2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D2">
-        <v>0</v>
+        <v>0.769</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G2">
         <v>0</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -550,13 +532,13 @@
         <v>0</v>
       </c>
       <c r="F3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H3">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -564,25 +546,25 @@
         <v>10</v>
       </c>
       <c r="B4">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="C4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D4">
-        <v>0</v>
+        <v>0.857</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G4">
         <v>0</v>
       </c>
       <c r="H4">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -590,25 +572,25 @@
         <v>11</v>
       </c>
       <c r="B5">
-        <v>0.625</v>
+        <v>1</v>
       </c>
       <c r="C5">
         <v>1</v>
       </c>
       <c r="D5">
-        <v>0.769</v>
+        <v>1</v>
       </c>
       <c r="E5">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F5">
+        <v>0</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5">
         <v>3</v>
-      </c>
-      <c r="G5">
-        <v>0</v>
-      </c>
-      <c r="H5">
-        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -616,25 +598,25 @@
         <v>12</v>
       </c>
       <c r="B6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C6">
-        <v>0</v>
+        <v>0.125</v>
       </c>
       <c r="D6">
-        <v>0</v>
+        <v>0.222</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F6">
         <v>0</v>
       </c>
       <c r="G6">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H6">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -642,25 +624,25 @@
         <v>13</v>
       </c>
       <c r="B7">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="C7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D7">
-        <v>0.857</v>
+        <v>0</v>
       </c>
       <c r="E7">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F7">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H7">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -671,19 +653,19 @@
         <v>1</v>
       </c>
       <c r="C8">
-        <v>1</v>
+        <v>0.667</v>
       </c>
       <c r="D8">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="E8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F8">
         <v>0</v>
       </c>
       <c r="G8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H8">
         <v>3</v>
@@ -706,168 +688,12 @@
         <v>0</v>
       </c>
       <c r="F9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G9">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8">
-      <c r="A10" t="s">
-        <v>16</v>
-      </c>
-      <c r="B10">
-        <v>1</v>
-      </c>
-      <c r="C10">
-        <v>0.125</v>
-      </c>
-      <c r="D10">
-        <v>0.222</v>
-      </c>
-      <c r="E10">
-        <v>1</v>
-      </c>
-      <c r="F10">
-        <v>0</v>
-      </c>
-      <c r="G10">
-        <v>7</v>
-      </c>
-      <c r="H10">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8">
-      <c r="A11" t="s">
-        <v>17</v>
-      </c>
-      <c r="B11">
-        <v>0</v>
-      </c>
-      <c r="C11">
-        <v>0</v>
-      </c>
-      <c r="D11">
-        <v>0</v>
-      </c>
-      <c r="E11">
-        <v>0</v>
-      </c>
-      <c r="F11">
-        <v>1</v>
-      </c>
-      <c r="G11">
-        <v>0</v>
-      </c>
-      <c r="H11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8">
-      <c r="A12" t="s">
-        <v>18</v>
-      </c>
-      <c r="B12">
-        <v>0</v>
-      </c>
-      <c r="C12">
-        <v>0</v>
-      </c>
-      <c r="D12">
-        <v>0</v>
-      </c>
-      <c r="E12">
-        <v>0</v>
-      </c>
-      <c r="F12">
-        <v>0</v>
-      </c>
-      <c r="G12">
-        <v>5</v>
-      </c>
-      <c r="H12">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8">
-      <c r="A13" t="s">
-        <v>19</v>
-      </c>
-      <c r="B13">
-        <v>1</v>
-      </c>
-      <c r="C13">
-        <v>0.667</v>
-      </c>
-      <c r="D13">
-        <v>0.8</v>
-      </c>
-      <c r="E13">
-        <v>2</v>
-      </c>
-      <c r="F13">
-        <v>0</v>
-      </c>
-      <c r="G13">
-        <v>1</v>
-      </c>
-      <c r="H13">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8">
-      <c r="A14" t="s">
-        <v>20</v>
-      </c>
-      <c r="B14">
-        <v>0</v>
-      </c>
-      <c r="C14">
-        <v>0</v>
-      </c>
-      <c r="D14">
-        <v>0</v>
-      </c>
-      <c r="E14">
-        <v>0</v>
-      </c>
-      <c r="F14">
-        <v>11</v>
-      </c>
-      <c r="G14">
-        <v>0</v>
-      </c>
-      <c r="H14">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8">
-      <c r="A15" t="s">
-        <v>21</v>
-      </c>
-      <c r="B15">
-        <v>0</v>
-      </c>
-      <c r="C15">
-        <v>0</v>
-      </c>
-      <c r="D15">
-        <v>0</v>
-      </c>
-      <c r="E15">
-        <v>0</v>
-      </c>
-      <c r="F15">
-        <v>0</v>
-      </c>
-      <c r="G15">
-        <v>5</v>
-      </c>
-      <c r="H15">
         <v>5</v>
       </c>
     </row>
@@ -883,31 +709,31 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>24</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -915,7 +741,7 @@
         <v>12</v>
       </c>
       <c r="B2" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C2">
         <v>93</v>
@@ -924,7 +750,7 @@
         <v>132</v>
       </c>
       <c r="E2" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -944,7 +770,7 @@
         <v>12</v>
       </c>
       <c r="B3" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="C3">
         <v>132</v>
@@ -953,7 +779,7 @@
         <v>208</v>
       </c>
       <c r="E3" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F3">
         <v>0</v>
@@ -980,31 +806,31 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>24</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -1012,7 +838,7 @@
         <v>13</v>
       </c>
       <c r="B2" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C2">
         <v>95</v>
@@ -1021,7 +847,7 @@
         <v>189</v>
       </c>
       <c r="E2" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -1041,7 +867,7 @@
         <v>13</v>
       </c>
       <c r="B3" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="C3">
         <v>189</v>
@@ -1050,7 +876,7 @@
         <v>218</v>
       </c>
       <c r="E3" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F3">
         <v>0</v>
@@ -1077,31 +903,31 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>24</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -1109,7 +935,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C2">
         <v>88</v>
@@ -1118,7 +944,7 @@
         <v>169</v>
       </c>
       <c r="E2" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -1138,7 +964,7 @@
         <v>14</v>
       </c>
       <c r="B3" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="C3">
         <v>169</v>
@@ -1147,7 +973,7 @@
         <v>220</v>
       </c>
       <c r="E3" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F3">
         <v>0</v>
@@ -1174,31 +1000,31 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>24</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -1206,7 +1032,7 @@
         <v>15</v>
       </c>
       <c r="B2" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C2">
         <v>19</v>
@@ -1215,7 +1041,7 @@
         <v>73</v>
       </c>
       <c r="E2" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -1235,7 +1061,7 @@
         <v>15</v>
       </c>
       <c r="B3" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C3">
         <v>73</v>
@@ -1244,7 +1070,7 @@
         <v>79</v>
       </c>
       <c r="E3" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F3">
         <v>0</v>
@@ -1264,7 +1090,7 @@
         <v>15</v>
       </c>
       <c r="B4" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C4">
         <v>79</v>
@@ -1273,7 +1099,7 @@
         <v>109</v>
       </c>
       <c r="E4" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F4">
         <v>0</v>
@@ -1300,31 +1126,31 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>24</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -1332,7 +1158,7 @@
         <v>16</v>
       </c>
       <c r="B2" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="C2">
         <v>31</v>
@@ -1341,7 +1167,7 @@
         <v>53</v>
       </c>
       <c r="E2" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -1361,7 +1187,7 @@
         <v>16</v>
       </c>
       <c r="B3" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C3">
         <v>53</v>
@@ -1370,7 +1196,7 @@
         <v>59</v>
       </c>
       <c r="E3" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="F3">
         <v>0</v>
@@ -1390,7 +1216,7 @@
         <v>16</v>
       </c>
       <c r="B4" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C4">
         <v>63</v>
@@ -1399,16 +1225,16 @@
         <v>130</v>
       </c>
       <c r="E4" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F4">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="G4">
-        <v>240</v>
+        <v>120</v>
       </c>
       <c r="H4">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="I4" t="b">
         <v>0</v>
@@ -1426,31 +1252,31 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>24</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -1458,7 +1284,7 @@
         <v>17</v>
       </c>
       <c r="B2" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C2">
         <v>30</v>
@@ -1467,7 +1293,7 @@
         <v>74</v>
       </c>
       <c r="E2" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -1487,7 +1313,7 @@
         <v>17</v>
       </c>
       <c r="B3" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="C3">
         <v>53</v>
@@ -1496,7 +1322,7 @@
         <v>74</v>
       </c>
       <c r="E3" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F3">
         <v>0</v>
@@ -1516,7 +1342,7 @@
         <v>17</v>
       </c>
       <c r="B4" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C4">
         <v>74</v>
@@ -1525,7 +1351,7 @@
         <v>110</v>
       </c>
       <c r="E4" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F4">
         <v>0</v>
@@ -1552,31 +1378,31 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>24</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -1584,7 +1410,7 @@
         <v>4</v>
       </c>
       <c r="B2" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C2">
         <v>0</v>
@@ -1592,17 +1418,8 @@
       <c r="D2">
         <v>36</v>
       </c>
-      <c r="E2" t="s">
-        <v>20</v>
-      </c>
-      <c r="F2">
-        <v>0</v>
-      </c>
-      <c r="G2">
-        <v>120</v>
-      </c>
       <c r="H2">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="I2" t="b">
         <v>0</v>
@@ -1613,7 +1430,7 @@
         <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C3">
         <v>36</v>
@@ -1621,17 +1438,8 @@
       <c r="D3">
         <v>40</v>
       </c>
-      <c r="E3" t="s">
-        <v>20</v>
-      </c>
-      <c r="F3">
-        <v>0</v>
-      </c>
-      <c r="G3">
-        <v>120</v>
-      </c>
       <c r="H3">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I3" t="b">
         <v>0</v>
@@ -1649,31 +1457,31 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>24</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -1681,7 +1489,7 @@
         <v>5</v>
       </c>
       <c r="B2" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C2">
         <v>0</v>
@@ -1689,17 +1497,8 @@
       <c r="D2">
         <v>44</v>
       </c>
-      <c r="E2" t="s">
-        <v>20</v>
-      </c>
-      <c r="F2">
-        <v>0</v>
-      </c>
-      <c r="G2">
-        <v>240</v>
-      </c>
       <c r="H2">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="I2" t="b">
         <v>0</v>
@@ -1710,7 +1509,7 @@
         <v>5</v>
       </c>
       <c r="B3" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C3">
         <v>44</v>
@@ -1718,17 +1517,8 @@
       <c r="D3">
         <v>123</v>
       </c>
-      <c r="E3" t="s">
-        <v>20</v>
-      </c>
-      <c r="F3">
-        <v>0</v>
-      </c>
-      <c r="G3">
-        <v>240</v>
-      </c>
       <c r="H3">
-        <v>79</v>
+        <v>0</v>
       </c>
       <c r="I3" t="b">
         <v>0</v>
@@ -1746,31 +1536,31 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>24</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -1778,7 +1568,7 @@
         <v>6</v>
       </c>
       <c r="B2" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C2">
         <v>0</v>
@@ -1786,17 +1576,8 @@
       <c r="D2">
         <v>52</v>
       </c>
-      <c r="E2" t="s">
-        <v>20</v>
-      </c>
-      <c r="F2">
-        <v>0</v>
-      </c>
-      <c r="G2">
-        <v>180</v>
-      </c>
       <c r="H2">
-        <v>52</v>
+        <v>0</v>
       </c>
       <c r="I2" t="b">
         <v>0</v>
@@ -1807,7 +1588,7 @@
         <v>6</v>
       </c>
       <c r="B3" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C3">
         <v>60</v>
@@ -1815,17 +1596,8 @@
       <c r="D3">
         <v>72</v>
       </c>
-      <c r="E3" t="s">
-        <v>20</v>
-      </c>
-      <c r="F3">
-        <v>0</v>
-      </c>
-      <c r="G3">
-        <v>180</v>
-      </c>
       <c r="H3">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="I3" t="b">
         <v>0</v>
@@ -1843,31 +1615,31 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>24</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -1875,7 +1647,7 @@
         <v>7</v>
       </c>
       <c r="B2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C2">
         <v>96</v>
@@ -1884,19 +1656,19 @@
         <v>105</v>
       </c>
       <c r="E2" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G2">
-        <v>120</v>
+        <v>240</v>
       </c>
       <c r="H2">
         <v>9</v>
       </c>
       <c r="I2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -1904,7 +1676,7 @@
         <v>7</v>
       </c>
       <c r="B3" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C3">
         <v>116</v>
@@ -1913,7 +1685,7 @@
         <v>160</v>
       </c>
       <c r="E3" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F3">
         <v>60</v>
@@ -1940,31 +1712,31 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>24</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -1972,7 +1744,7 @@
         <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C2">
         <v>60</v>
@@ -1981,19 +1753,19 @@
         <v>77</v>
       </c>
       <c r="E2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F2">
         <v>0</v>
       </c>
       <c r="G2">
-        <v>120</v>
+        <v>180</v>
       </c>
       <c r="H2">
         <v>17</v>
       </c>
       <c r="I2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -2008,31 +1780,31 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>24</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -2040,7 +1812,7 @@
         <v>9</v>
       </c>
       <c r="B2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C2">
         <v>114</v>
@@ -2049,19 +1821,19 @@
         <v>138</v>
       </c>
       <c r="E2" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="G2">
-        <v>180</v>
+        <v>240</v>
       </c>
       <c r="H2">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="I2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -2076,31 +1848,31 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>24</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -2108,7 +1880,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C2">
         <v>14</v>
@@ -2117,7 +1889,7 @@
         <v>100</v>
       </c>
       <c r="E2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -2144,31 +1916,31 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>24</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -2176,7 +1948,7 @@
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C2">
         <v>37</v>
@@ -2185,7 +1957,7 @@
         <v>100</v>
       </c>
       <c r="E2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F2">
         <v>0</v>

--- a/data/analysis_panns/sound_class_eval_panns_w5_0s_h2_5s.xlsx
+++ b/data/analysis_panns/sound_class_eval_panns_w5_0s_h2_5s.xlsx
@@ -22,13 +22,19 @@
     <sheet name="Scene_15" sheetId="13" r:id="rId13"/>
     <sheet name="Scene_16" sheetId="14" r:id="rId14"/>
     <sheet name="Scene_17" sheetId="15" r:id="rId15"/>
+    <sheet name="Scene_29" sheetId="16" r:id="rId16"/>
+    <sheet name="Scene_30" sheetId="17" r:id="rId17"/>
+    <sheet name="Scene_31" sheetId="18" r:id="rId18"/>
+    <sheet name="Scene_32" sheetId="19" r:id="rId19"/>
+    <sheet name="Scene_33" sheetId="20" r:id="rId20"/>
+    <sheet name="Scene_34" sheetId="21" r:id="rId21"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="267" uniqueCount="25">
   <si>
     <t>class</t>
   </si>
@@ -1371,6 +1377,396 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:I4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:9">
+      <c r="A1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2">
+        <v>29</v>
+      </c>
+      <c r="B2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2">
+        <v>0</v>
+      </c>
+      <c r="D2">
+        <v>35</v>
+      </c>
+      <c r="H2">
+        <v>0</v>
+      </c>
+      <c r="I2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
+      <c r="A3">
+        <v>29</v>
+      </c>
+      <c r="B3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3">
+        <v>36</v>
+      </c>
+      <c r="D3">
+        <v>37</v>
+      </c>
+      <c r="H3">
+        <v>0</v>
+      </c>
+      <c r="I3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
+      <c r="A4">
+        <v>29</v>
+      </c>
+      <c r="B4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4">
+        <v>50</v>
+      </c>
+      <c r="D4">
+        <v>52</v>
+      </c>
+      <c r="H4">
+        <v>0</v>
+      </c>
+      <c r="I4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:I3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:9">
+      <c r="A1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2">
+        <v>30</v>
+      </c>
+      <c r="B2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2">
+        <v>4</v>
+      </c>
+      <c r="D2">
+        <v>10</v>
+      </c>
+      <c r="E2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>180</v>
+      </c>
+      <c r="H2">
+        <v>6</v>
+      </c>
+      <c r="I2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
+      <c r="A3">
+        <v>30</v>
+      </c>
+      <c r="B3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3">
+        <v>10</v>
+      </c>
+      <c r="D3">
+        <v>122</v>
+      </c>
+      <c r="E3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F3">
+        <v>0</v>
+      </c>
+      <c r="G3">
+        <v>180</v>
+      </c>
+      <c r="H3">
+        <v>112</v>
+      </c>
+      <c r="I3" t="b">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:I3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:9">
+      <c r="A1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2">
+        <v>31</v>
+      </c>
+      <c r="B2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2">
+        <v>108</v>
+      </c>
+      <c r="D2">
+        <v>138</v>
+      </c>
+      <c r="E2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2">
+        <v>60</v>
+      </c>
+      <c r="G2">
+        <v>240</v>
+      </c>
+      <c r="H2">
+        <v>30</v>
+      </c>
+      <c r="I2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
+      <c r="A3">
+        <v>31</v>
+      </c>
+      <c r="B3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3">
+        <v>138</v>
+      </c>
+      <c r="D3">
+        <v>240</v>
+      </c>
+      <c r="E3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3">
+        <v>60</v>
+      </c>
+      <c r="G3">
+        <v>240</v>
+      </c>
+      <c r="H3">
+        <v>102</v>
+      </c>
+      <c r="I3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:I3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:9">
+      <c r="A1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2">
+        <v>32</v>
+      </c>
+      <c r="B2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2">
+        <v>103</v>
+      </c>
+      <c r="D2">
+        <v>138</v>
+      </c>
+      <c r="E2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>240</v>
+      </c>
+      <c r="H2">
+        <v>35</v>
+      </c>
+      <c r="I2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
+      <c r="A3">
+        <v>32</v>
+      </c>
+      <c r="B3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3">
+        <v>138</v>
+      </c>
+      <c r="D3">
+        <v>182</v>
+      </c>
+      <c r="E3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3">
+        <v>0</v>
+      </c>
+      <c r="G3">
+        <v>240</v>
+      </c>
+      <c r="H3">
+        <v>44</v>
+      </c>
+      <c r="I3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:I3"/>
@@ -1440,6 +1836,200 @@
       </c>
       <c r="H3">
         <v>0</v>
+      </c>
+      <c r="I3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:I3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:9">
+      <c r="A1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2">
+        <v>33</v>
+      </c>
+      <c r="B2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2">
+        <v>28</v>
+      </c>
+      <c r="D2">
+        <v>62</v>
+      </c>
+      <c r="E2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>120</v>
+      </c>
+      <c r="H2">
+        <v>34</v>
+      </c>
+      <c r="I2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
+      <c r="A3">
+        <v>33</v>
+      </c>
+      <c r="B3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3">
+        <v>63</v>
+      </c>
+      <c r="D3">
+        <v>103</v>
+      </c>
+      <c r="E3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F3">
+        <v>0</v>
+      </c>
+      <c r="G3">
+        <v>120</v>
+      </c>
+      <c r="H3">
+        <v>40</v>
+      </c>
+      <c r="I3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:I3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:9">
+      <c r="A1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2">
+        <v>34</v>
+      </c>
+      <c r="B2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2">
+        <v>0</v>
+      </c>
+      <c r="D2">
+        <v>50</v>
+      </c>
+      <c r="E2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>120</v>
+      </c>
+      <c r="H2">
+        <v>50</v>
+      </c>
+      <c r="I2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
+      <c r="A3">
+        <v>34</v>
+      </c>
+      <c r="B3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3">
+        <v>50</v>
+      </c>
+      <c r="D3">
+        <v>120</v>
+      </c>
+      <c r="E3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F3">
+        <v>0</v>
+      </c>
+      <c r="G3">
+        <v>120</v>
+      </c>
+      <c r="H3">
+        <v>70</v>
       </c>
       <c r="I3" t="b">
         <v>0</v>
